--- a/output/pdf_financials_xlsx/SAWC.P.xlsx
+++ b/output/pdf_financials_xlsx/SAWC.P.xlsx
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.472676</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.419142</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.288074</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.232453</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.203092</v>
       </c>
     </row>
     <row r="35">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.472676</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.419142</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.288074</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.232453</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.203092</v>
       </c>
     </row>
     <row r="37">
@@ -1732,13 +1732,13 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.2936</v>
+        <v>0.005526</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.233446</v>
+        <v>0.000993</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.204545</v>
+        <v>0.001453</v>
       </c>
     </row>
     <row r="49">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/pdf_financials_xlsx/SAWC.P.xlsx
+++ b/output/pdf_financials_xlsx/SAWC.P.xlsx
@@ -6158,7 +6158,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -6764,7 +6768,11 @@
           <t>Proceeds from share issuance 6</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
         <v>0.5614980000000001</v>
       </c>
